--- a/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
+++ b/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,10 @@
     <font>
       <b val="1"/>
       <color rgb="00D93025"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -76,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -85,6 +89,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -452,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -552,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -582,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -590,51 +597,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -706,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -745,11 +748,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -779,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -809,7 +812,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -817,10 +820,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -829,39 +830,37 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -895,11 +894,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -929,12 +928,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -959,7 +958,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -967,10 +966,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -979,39 +976,37 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1036,7 +1031,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1044,8 +1039,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>2</v>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1054,37 +1051,39 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1156,12 +1155,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1186,7 +1185,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1194,10 +1193,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1206,39 +1203,37 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1310,12 +1305,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1340,7 +1335,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1348,51 +1343,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1417,7 +1408,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1425,8 +1416,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1435,37 +1428,39 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1490,7 +1485,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1498,10 +1493,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1510,39 +1503,37 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1567,7 +1558,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1575,47 +1566,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1687,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1717,7 +1712,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1725,8 +1720,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n">
-        <v>1</v>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
@@ -1735,37 +1732,39 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1837,12 +1836,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1867,7 +1866,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1875,10 +1874,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1887,39 +1884,37 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1991,12 +1986,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2021,7 +2016,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2029,51 +2024,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2145,12 +2136,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2175,7 +2166,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2183,10 +2174,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2195,39 +2184,37 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2299,12 +2286,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2376,12 +2363,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2453,12 +2440,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2530,12 +2517,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2607,12 +2594,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2684,12 +2671,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2761,12 +2748,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2838,12 +2825,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2868,7 +2855,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2876,8 +2863,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>0</v>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
@@ -2886,37 +2875,39 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2988,12 +2979,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3018,7 +3009,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -3026,8 +3017,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n">
-        <v>0</v>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3036,37 +3029,39 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3138,12 +3133,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3215,12 +3210,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3292,12 +3287,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3322,7 +3317,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3330,10 +3325,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3342,39 +3335,37 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3446,12 +3437,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3476,7 +3467,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3484,10 +3475,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3496,39 +3485,37 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3600,12 +3587,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3677,12 +3664,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3754,12 +3741,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3831,12 +3818,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3908,12 +3895,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3938,7 +3925,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3946,8 +3933,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3956,37 +3945,39 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4011,7 +4002,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -4019,8 +4010,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n">
-        <v>0</v>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
@@ -4029,37 +4022,39 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4084,7 +4079,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4092,8 +4087,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4102,37 +4099,39 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4157,7 +4156,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4165,47 +4164,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4230,7 +4233,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4238,8 +4241,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n">
-        <v>0</v>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4248,37 +4253,39 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4303,7 +4310,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4311,8 +4318,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>1</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4321,37 +4330,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4376,7 +4387,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4384,10 +4395,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4396,39 +4405,37 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4453,7 +4460,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4461,10 +4468,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4473,39 +4478,37 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4530,7 +4533,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4538,10 +4541,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4550,39 +4551,37 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4607,7 +4606,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4615,51 +4614,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4684,7 +4679,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4692,10 +4687,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4704,39 +4697,37 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4761,7 +4752,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4769,10 +4760,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I57" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
@@ -4781,39 +4770,37 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4885,12 +4872,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4962,12 +4949,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5039,12 +5026,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5116,12 +5103,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5146,7 +5133,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5154,8 +5141,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5164,37 +5153,39 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5266,12 +5257,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5296,7 +5287,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5304,47 +5295,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5416,12 +5411,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5446,7 +5441,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5454,8 +5449,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>1</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5464,37 +5461,39 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5566,12 +5565,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5607,9 +5606,9 @@
       <c r="I68" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5639,12 +5638,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5716,12 +5715,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5755,11 +5754,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5789,12 +5788,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5866,12 +5865,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5939,12 +5938,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6016,12 +6015,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6089,12 +6088,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6119,7 +6118,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6127,8 +6126,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
@@ -6137,37 +6138,39 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6201,11 +6204,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6235,78 +6238,524 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-043</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
-        <is>
-          <t>Tombola</t>
-        </is>
-      </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>4078816754</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="n">
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L77" s="2" t="n">
+      <c r="L83" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M77" s="2" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="N83" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O77" s="2" t="inlineStr">
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O77"/>
+  <autoFilter ref="A1:O83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
+++ b/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -589,33 +589,33 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,14 +709,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -739,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -748,24 +748,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,14 +782,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -812,7 +812,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -820,8 +820,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -830,39 +832,41 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -894,11 +898,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -928,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1001,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1031,7 +1035,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1039,10 +1043,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1051,41 +1053,39 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1116,10 +1116,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1128,41 +1126,39 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1185,7 +1181,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1193,8 +1189,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1203,37 +1201,39 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1346,9 +1346,9 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1378,12 +1378,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1455,14 +1455,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1494,11 +1494,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1605,14 +1605,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1643,10 +1643,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1655,39 +1653,37 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1755,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1836,14 +1832,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1866,7 +1862,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1874,8 +1870,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1884,37 +1882,39 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1986,12 +1986,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2027,9 +2027,9 @@
       <c r="I21" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2059,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2136,14 +2136,14 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2175,11 +2175,11 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2286,14 +2286,14 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2324,10 +2324,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2336,39 +2334,37 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2440,12 +2436,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2517,12 +2513,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2594,12 +2590,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2671,12 +2667,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2748,12 +2744,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2825,12 +2821,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2902,12 +2898,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2979,12 +2975,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3056,12 +3052,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3133,12 +3129,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3210,12 +3206,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3287,14 +3283,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3317,7 +3313,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3325,8 +3321,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n">
-        <v>0</v>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3335,37 +3333,39 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3587,14 +3587,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3625,10 +3625,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3637,39 +3635,37 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3741,12 +3737,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3818,12 +3814,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3895,12 +3891,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3972,12 +3968,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4049,12 +4045,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4126,12 +4122,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4203,12 +4199,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4280,12 +4276,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4357,14 +4353,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4387,7 +4383,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4395,8 +4391,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4405,39 +4403,41 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4468,8 +4468,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n">
-        <v>0</v>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
@@ -4478,37 +4480,39 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4576,12 +4580,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4617,9 +4621,9 @@
       <c r="I55" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -4649,12 +4653,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4722,14 +4726,14 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4761,11 +4765,11 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -4795,14 +4799,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4825,7 +4829,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4833,10 +4837,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4845,41 +4847,39 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4910,10 +4910,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I59" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4922,39 +4920,37 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5026,12 +5022,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5103,12 +5099,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5180,12 +5176,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5257,12 +5253,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5334,12 +5330,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5411,12 +5407,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5488,12 +5484,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5565,14 +5561,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5595,7 +5591,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5603,8 +5599,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5613,37 +5611,39 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5756,9 +5756,9 @@
       <c r="I70" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5865,14 +5865,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5904,11 +5904,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6015,14 +6015,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6054,11 +6054,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6165,14 +6165,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6204,11 +6204,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6388,12 +6388,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6465,14 +6465,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6504,11 +6504,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6538,14 +6538,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6568,7 +6568,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6576,8 +6576,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6586,39 +6588,41 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6650,11 +6654,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6684,12 +6688,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6754,8 +6758,154 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O83"/>
+  <autoFilter ref="A1:O85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
+++ b/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -592,17 +592,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -748,24 +748,24 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -970,8 +970,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -980,37 +982,39 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1038,9 +1042,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
@@ -1048,7 +1052,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1078,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1108,7 +1112,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1116,8 +1120,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1126,37 +1132,39 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1181,7 +1189,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1189,51 +1197,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1305,12 +1309,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1344,11 +1348,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1378,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1408,7 +1412,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1416,10 +1420,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1428,39 +1430,37 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1494,11 +1494,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1528,12 +1528,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1566,10 +1566,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1578,39 +1576,37 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1635,7 +1631,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1643,8 +1639,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>2</v>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1653,37 +1651,39 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1755,12 +1755,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1793,10 +1793,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1805,39 +1803,37 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1905,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1939,7 +1935,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1947,51 +1943,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2016,7 +2008,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2024,8 +2016,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2034,37 +2028,39 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2089,7 +2085,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2097,10 +2093,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2109,39 +2103,37 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2166,7 +2158,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2174,47 +2166,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2286,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2316,7 +2312,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2324,8 +2320,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>1</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2334,37 +2332,39 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2436,12 +2436,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2474,10 +2474,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2486,39 +2484,37 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2590,12 +2586,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2620,7 +2616,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2628,51 +2624,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2744,12 +2736,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2774,7 +2766,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2782,10 +2774,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2794,39 +2784,37 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2898,12 +2886,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2975,12 +2963,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3052,12 +3040,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3129,12 +3117,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3206,12 +3194,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3283,12 +3271,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3360,12 +3348,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3437,12 +3425,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3467,7 +3455,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3475,8 +3463,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n">
-        <v>0</v>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3485,37 +3475,39 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3587,12 +3579,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3617,7 +3609,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3625,8 +3617,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>0</v>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3635,37 +3629,39 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3737,12 +3733,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3814,12 +3810,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3891,12 +3887,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3921,7 +3917,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3929,10 +3925,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3941,39 +3935,37 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4045,12 +4037,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4075,7 +4067,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4083,10 +4075,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4095,39 +4085,37 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4199,12 +4187,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4276,12 +4264,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4353,12 +4341,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4430,12 +4418,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4507,12 +4495,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4537,7 +4525,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4545,8 +4533,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4555,37 +4545,39 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4610,7 +4602,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4618,8 +4610,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n">
-        <v>0</v>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
@@ -4628,37 +4622,39 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4683,7 +4679,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4691,8 +4687,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4701,37 +4699,39 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4764,47 +4764,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4829,7 +4833,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4837,8 +4841,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n">
-        <v>0</v>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4847,37 +4853,39 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4902,7 +4910,7 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -4910,8 +4918,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n">
-        <v>1</v>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
@@ -4920,37 +4930,39 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4975,7 +4987,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4983,10 +4995,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4995,39 +5005,37 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5052,7 +5060,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5060,10 +5068,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5072,39 +5078,37 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5129,7 +5133,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5137,10 +5141,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5149,39 +5151,37 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5214,51 +5214,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5283,7 +5279,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5291,10 +5287,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5303,39 +5297,37 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5360,7 +5352,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5368,10 +5360,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I65" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5380,39 +5370,37 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5484,12 +5472,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5561,12 +5549,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5638,12 +5626,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5715,12 +5703,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5745,7 +5733,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5753,8 +5741,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5763,37 +5753,39 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5865,12 +5857,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5895,7 +5887,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5903,47 +5895,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6015,12 +6011,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6045,7 +6041,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -6053,8 +6049,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n">
-        <v>1</v>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -6063,37 +6061,39 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6206,9 +6206,9 @@
       <c r="I76" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6354,11 +6354,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6388,12 +6388,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6465,12 +6465,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6538,12 +6538,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6615,12 +6615,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6726,8 +6726,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6736,37 +6738,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6800,11 +6804,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6834,78 +6838,524 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-043</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Tombola</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>4078816754</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="n">
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L85" s="2" t="n">
+      <c r="L91" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M85" s="2" t="inlineStr">
+      <c r="M91" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="N91" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O85" s="2" t="inlineStr">
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
+++ b/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -748,11 +748,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -820,10 +820,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -832,39 +830,37 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -898,7 +894,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -932,12 +928,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -962,7 +958,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -970,10 +966,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -982,39 +976,37 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1042,17 +1034,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1074,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1151,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1189,7 +1181,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1198,24 +1190,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1232,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1301,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1382,12 +1374,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1412,7 +1404,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1420,8 +1412,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1430,37 +1424,39 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1488,9 +1484,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
@@ -1498,7 +1494,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1528,12 +1524,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1558,7 +1554,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1566,8 +1562,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n">
-        <v>0</v>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1576,37 +1574,39 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1639,51 +1639,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1755,12 +1751,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1794,11 +1790,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1828,12 +1824,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1858,7 +1854,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1866,10 +1862,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1878,39 +1872,37 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1944,11 +1936,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1978,12 +1970,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2008,7 +2000,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2016,10 +2008,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2028,39 +2018,37 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2085,7 +2073,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2093,8 +2081,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>2</v>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2103,37 +2093,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2205,12 +2197,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2235,7 +2227,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2243,10 +2235,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2255,39 +2245,37 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,12 +2347,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2389,7 +2377,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2397,51 +2385,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2466,7 +2450,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2474,8 +2458,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2484,37 +2470,39 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2539,7 +2527,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2547,10 +2535,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I28" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
@@ -2559,39 +2545,37 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2616,7 +2600,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2624,47 +2608,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2736,12 +2724,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2766,7 +2754,7 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2774,8 +2762,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n">
-        <v>1</v>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
@@ -2784,37 +2774,39 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2886,12 +2878,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2916,7 +2908,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2924,10 +2916,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2936,39 +2926,37 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3040,12 +3028,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3070,7 +3058,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3078,51 +3066,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3194,12 +3178,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3224,7 +3208,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3232,10 +3216,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3244,39 +3226,37 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3348,12 +3328,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3425,12 +3405,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3502,12 +3482,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3579,12 +3559,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3656,12 +3636,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3733,12 +3713,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3810,12 +3790,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3887,12 +3867,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3917,7 +3897,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3925,8 +3905,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n">
-        <v>0</v>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3935,37 +3917,39 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4037,12 +4021,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4067,7 +4051,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4075,8 +4059,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n">
-        <v>0</v>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -4085,37 +4071,39 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4187,12 +4175,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4264,12 +4252,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4341,12 +4329,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4371,7 +4359,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4379,10 +4367,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4391,39 +4377,37 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4495,12 +4479,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4525,7 +4509,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4533,10 +4517,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4545,39 +4527,37 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4649,12 +4629,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4726,12 +4706,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4803,12 +4783,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4880,12 +4860,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4957,12 +4937,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4987,7 +4967,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4995,8 +4975,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -5005,37 +4987,39 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5060,7 +5044,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -5068,8 +5052,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n">
-        <v>0</v>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
@@ -5078,37 +5064,39 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5133,7 +5121,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5141,8 +5129,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>0</v>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
@@ -5151,37 +5141,39 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5206,7 +5198,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5214,47 +5206,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5279,7 +5275,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -5287,8 +5283,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>0</v>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
@@ -5297,37 +5295,39 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5360,8 +5360,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>1</v>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
@@ -5370,37 +5372,39 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5425,7 +5429,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5433,10 +5437,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5445,39 +5447,37 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5502,7 +5502,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5510,10 +5510,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5522,39 +5520,37 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5579,7 +5575,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5587,10 +5583,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5599,39 +5593,37 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5656,7 +5648,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5664,51 +5656,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5733,7 +5721,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5741,10 +5729,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5753,39 +5739,37 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5810,7 +5794,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5818,10 +5802,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I71" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
@@ -5830,39 +5812,37 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5934,12 +5914,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6011,12 +5991,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6088,12 +6068,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6165,12 +6145,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6195,7 +6175,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6203,8 +6183,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
-        <v>0</v>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6213,37 +6195,39 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6315,12 +6299,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6345,7 +6329,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6353,47 +6337,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6465,12 +6453,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6495,7 +6483,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6503,8 +6491,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n">
-        <v>1</v>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6513,37 +6503,39 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6615,12 +6607,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6656,9 +6648,9 @@
       <c r="I82" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6688,12 +6680,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6765,12 +6757,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6804,11 +6796,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6838,12 +6830,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6915,12 +6907,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6988,12 +6980,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7065,12 +7057,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7138,12 +7130,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7168,7 +7160,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -7176,8 +7168,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n">
-        <v>0</v>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
@@ -7186,37 +7180,39 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7250,11 +7246,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7284,78 +7280,524 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-043</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Tombola</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>4078816754</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="n">
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L91" s="2" t="n">
+      <c r="L97" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M91" s="2" t="inlineStr">
+      <c r="M97" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="N97" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O91" s="2" t="inlineStr">
+      <c r="O97" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O91"/>
+  <autoFilter ref="A1:O97"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
+++ b/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -750,9 +750,9 @@
       <c r="I4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,14 +782,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -812,7 +812,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -820,8 +820,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -830,39 +832,41 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -894,11 +898,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -928,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1001,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1040,11 +1044,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1074,14 +1078,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1104,7 +1108,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1112,10 +1116,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1124,41 +1126,39 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1190,11 +1190,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1301,14 +1301,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1340,11 +1340,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1374,12 +1374,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1451,14 +1451,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1484,17 +1484,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1524,12 +1524,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1601,14 +1601,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1631,33 +1631,33 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L16" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1751,14 +1751,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1790,24 +1790,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1824,14 +1824,14 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1862,8 +1862,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
@@ -1872,39 +1874,41 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1936,11 +1940,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1970,12 +1974,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2043,14 +2047,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2081,10 +2085,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I22" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2093,41 +2095,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2158,10 +2158,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2170,41 +2168,39 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2227,7 +2223,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2235,8 +2231,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2245,37 +2243,39 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2347,12 +2347,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2388,9 +2388,9 @@
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2497,14 +2497,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2536,11 +2536,11 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2570,12 +2570,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2647,14 +2647,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2685,10 +2685,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I30" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2697,39 +2695,37 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2801,12 +2797,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2878,14 +2874,14 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2908,7 +2904,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -2916,8 +2912,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n">
-        <v>0</v>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
@@ -2926,37 +2924,39 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3069,9 +3069,9 @@
       <c r="I35" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -3101,12 +3101,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3178,14 +3178,14 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3217,11 +3217,11 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3328,14 +3328,14 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3366,10 +3366,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I39" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3378,39 +3376,37 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3482,12 +3478,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3559,12 +3555,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3636,12 +3632,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3713,12 +3709,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3790,12 +3786,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3867,12 +3863,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3944,12 +3940,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4021,12 +4017,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4098,12 +4094,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4175,12 +4171,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4252,12 +4248,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4329,14 +4325,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4359,7 +4355,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4367,8 +4363,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n">
-        <v>0</v>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4377,37 +4375,39 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4629,14 +4629,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4667,10 +4667,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4679,39 +4677,37 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4783,12 +4779,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4860,12 +4856,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4937,12 +4933,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5014,12 +5010,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5091,12 +5087,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5168,12 +5164,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5245,12 +5241,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5322,12 +5318,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5399,14 +5395,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5429,7 +5425,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5437,8 +5433,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>0</v>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
@@ -5447,39 +5445,41 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5510,8 +5510,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>0</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5520,37 +5522,39 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5618,12 +5622,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5659,9 +5663,9 @@
       <c r="I69" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -5691,12 +5695,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5764,14 +5768,14 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5803,11 +5807,11 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -5837,14 +5841,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5867,7 +5871,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5875,10 +5879,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I72" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5887,41 +5889,39 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5952,10 +5952,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I73" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5964,39 +5962,37 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6068,12 +6064,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6145,12 +6141,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6222,12 +6218,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6299,12 +6295,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6376,12 +6372,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6453,12 +6449,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6530,12 +6526,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6607,14 +6603,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6637,7 +6633,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6645,8 +6641,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n">
-        <v>0</v>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6655,37 +6653,39 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6798,9 +6798,9 @@
       <c r="I84" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6907,14 +6907,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6946,11 +6946,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7057,14 +7057,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7096,11 +7096,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7130,12 +7130,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7207,14 +7207,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7246,11 +7246,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7280,12 +7280,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7357,12 +7357,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7430,12 +7430,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7507,14 +7507,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7546,11 +7546,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7580,14 +7580,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7610,7 +7610,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7618,8 +7618,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
-        <v>0</v>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7628,39 +7630,41 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7692,11 +7696,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7726,12 +7730,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7796,8 +7800,154 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O97"/>
+  <autoFilter ref="A1:O99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
+++ b/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:O103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 50,0%</t>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -898,11 +898,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>3</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -970,8 +970,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -980,37 +982,39 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1044,11 +1048,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1078,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1108,7 +1112,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1116,8 +1120,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
@@ -1126,37 +1132,39 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1190,11 +1198,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▼ 80,0%</t>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1224,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1254,7 +1262,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1262,10 +1270,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1274,39 +1280,37 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1340,11 +1344,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1374,12 +1378,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1404,7 +1408,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1412,10 +1416,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1424,39 +1426,37 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1490,11 +1490,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1524,12 +1524,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1634,17 +1634,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>5</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1751,12 +1751,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1790,24 +1790,24 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>6</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1934,17 +1934,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1974,12 +1974,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2012,8 +2012,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
@@ -2022,37 +2024,39 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2077,7 +2081,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2088,22 +2092,22 @@
       <c r="I22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2120,12 +2124,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2150,7 +2154,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2158,8 +2162,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
@@ -2168,37 +2174,39 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2223,7 +2231,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2231,51 +2239,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I24" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2300,7 +2304,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2308,10 +2312,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2320,39 +2322,37 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2420,12 +2420,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2458,10 +2458,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2470,39 +2468,37 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2527,7 +2523,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2535,47 +2531,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2647,12 +2647,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
@@ -2720,12 +2720,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2835,51 +2835,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2951,12 +2947,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2981,7 +2977,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2989,10 +2985,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I34" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
@@ -3001,39 +2995,37 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3058,7 +3050,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3066,8 +3058,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3076,37 +3070,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3178,12 +3174,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3208,7 +3204,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3216,47 +3212,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3401,12 +3401,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3516,51 +3516,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3632,12 +3628,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3662,7 +3658,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3670,10 +3666,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I43" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3682,39 +3676,37 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3786,12 +3778,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3863,12 +3855,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3940,12 +3932,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4017,12 +4009,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4094,12 +4086,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4171,12 +4163,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4248,12 +4240,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4325,12 +4317,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4402,12 +4394,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4479,12 +4471,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4509,7 +4501,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4517,8 +4509,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n">
-        <v>0</v>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4527,37 +4521,39 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4629,12 +4625,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4659,7 +4655,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4667,8 +4663,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n">
-        <v>0</v>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4677,37 +4675,39 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4817,10 +4817,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4829,39 +4827,37 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4933,12 +4929,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4963,7 +4959,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4971,10 +4967,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4983,39 +4977,37 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5087,12 +5079,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5164,12 +5156,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5241,12 +5233,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5318,12 +5310,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5395,12 +5387,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5472,12 +5464,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5549,12 +5541,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5579,7 +5571,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5587,8 +5579,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n">
-        <v>0</v>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
@@ -5597,37 +5591,39 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5652,7 +5648,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5660,8 +5656,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n">
-        <v>0</v>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
@@ -5670,37 +5668,39 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5733,8 +5733,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n">
-        <v>0</v>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
@@ -5743,37 +5745,39 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5798,7 +5802,7 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5806,47 +5810,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5914,12 +5922,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5953,7 +5961,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5987,12 +5995,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6017,7 +6025,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -6025,10 +6033,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -6037,39 +6043,37 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6094,7 +6098,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6102,51 +6106,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I75" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6179,10 +6179,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I76" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6191,39 +6189,37 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6248,7 +6244,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6256,10 +6252,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6268,39 +6262,37 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6372,12 +6364,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6449,12 +6441,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6526,12 +6518,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6603,12 +6595,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6680,12 +6672,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6757,12 +6749,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6787,7 +6779,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6795,8 +6787,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="2" t="n">
-        <v>0</v>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6805,37 +6799,39 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6907,12 +6903,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6937,7 +6933,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -6945,47 +6941,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -7130,12 +7130,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7207,12 +7207,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7280,12 +7280,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7357,12 +7357,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7430,12 +7430,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7546,11 +7546,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7580,12 +7580,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7657,12 +7657,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7696,11 +7696,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7768,8 +7768,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7778,37 +7780,39 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>03/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7842,7 +7846,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7876,78 +7880,374 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-043</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Tombola</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>4078816754</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="n">
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L99" s="2" t="n">
+      <c r="L103" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M99" s="2" t="inlineStr">
+      <c r="M103" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N99" s="2" t="inlineStr">
+      <c r="N103" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O99" s="2" t="inlineStr">
+      <c r="O103" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O99"/>
+  <autoFilter ref="A1:O103"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
+++ b/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>▲ 166,7%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -748,11 +748,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -898,11 +898,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1048,11 +1048,11 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1082,12 +1082,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1198,11 +1198,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1270,8 +1270,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1280,37 +1282,39 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1338,17 +1342,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1378,12 +1382,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1408,7 +1412,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1416,8 +1420,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1426,37 +1432,39 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1481,7 +1489,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1490,24 +1498,24 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1524,12 +1532,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1601,12 +1609,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1640,11 +1648,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1674,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1751,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1790,11 +1798,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1824,12 +1832,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1901,12 +1909,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1934,9 +1942,9 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
@@ -1974,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2051,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2081,12 +2089,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
@@ -2094,20 +2102,20 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L22" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2124,12 +2132,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2201,12 +2209,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2231,7 +2239,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 24,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2240,24 +2248,24 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2274,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2304,7 +2312,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -2312,8 +2320,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n">
-        <v>0</v>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
@@ -2322,37 +2332,39 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2386,11 +2398,11 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>8</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2420,12 +2432,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2450,7 +2462,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -2458,8 +2470,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n">
-        <v>0</v>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2468,37 +2482,39 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2523,7 +2539,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2531,51 +2547,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I28" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2647,12 +2659,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2686,11 +2698,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>3</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2720,12 +2732,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2797,12 +2809,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2836,11 +2848,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2870,12 +2882,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2947,12 +2959,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2988,9 +3000,9 @@
       <c r="I34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3020,12 +3032,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3050,7 +3062,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3058,10 +3070,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3070,39 +3080,37 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3127,7 +3135,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3135,51 +3143,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I36" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3204,7 +3208,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3212,10 +3216,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3224,39 +3226,37 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3289,51 +3289,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3358,7 +3354,7 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3366,8 +3362,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n">
-        <v>0</v>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3376,37 +3374,39 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3439,51 +3439,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I40" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3508,7 +3504,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3516,47 +3512,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3589,51 +3589,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I42" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3658,7 +3654,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3666,8 +3662,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n">
-        <v>1</v>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3676,37 +3674,39 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3731,59 +3731,55 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3855,12 +3851,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3885,7 +3881,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3893,51 +3889,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4009,12 +4001,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4039,7 +4031,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4047,51 +4039,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I48" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4116,7 +4104,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4124,10 +4112,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4136,39 +4122,37 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4193,7 +4177,7 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -4201,10 +4185,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I50" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4213,39 +4195,37 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4270,7 +4250,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4278,10 +4258,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4290,39 +4268,37 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4394,12 +4370,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4471,12 +4447,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4501,7 +4477,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4509,10 +4485,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4521,39 +4495,37 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4625,12 +4597,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4655,7 +4627,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4663,51 +4635,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4779,12 +4747,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4818,7 +4786,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
@@ -4852,12 +4820,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4929,12 +4897,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4959,7 +4927,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4967,8 +4935,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n">
-        <v>0</v>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -4977,37 +4947,39 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5079,12 +5051,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5156,12 +5128,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5186,7 +5158,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5194,10 +5166,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5206,39 +5176,37 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5310,12 +5278,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5340,7 +5308,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5348,51 +5316,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5464,12 +5428,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5494,7 +5458,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5502,10 +5466,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5514,39 +5476,37 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5618,12 +5578,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5695,12 +5655,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5772,12 +5732,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5849,12 +5809,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5879,7 +5839,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5887,8 +5847,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n">
-        <v>0</v>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
@@ -5897,37 +5859,39 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5952,7 +5916,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -5960,8 +5924,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
@@ -5970,37 +5936,39 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6025,7 +5993,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -6033,8 +6001,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n">
-        <v>0</v>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
@@ -6043,37 +6013,39 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6098,7 +6070,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -6106,47 +6078,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6171,7 +6147,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6179,8 +6155,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n">
-        <v>0</v>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6189,37 +6167,39 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6244,7 +6224,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6252,8 +6232,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>1</v>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6262,37 +6244,39 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6364,12 +6348,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6441,12 +6425,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6518,12 +6502,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6595,12 +6579,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6625,7 +6609,7 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -6633,10 +6617,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I82" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
@@ -6645,39 +6627,37 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6749,12 +6729,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6779,7 +6759,7 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -6787,10 +6767,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I84" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
@@ -6799,39 +6777,37 @@
       </c>
       <c r="K84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6903,12 +6879,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6980,12 +6956,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7057,12 +7033,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7087,7 +7063,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -7095,8 +7071,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="n">
-        <v>0</v>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
@@ -7105,37 +7083,39 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7207,12 +7187,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7237,7 +7217,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7245,47 +7225,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7357,12 +7341,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7387,7 +7371,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7395,8 +7379,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="n">
-        <v>1</v>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7405,37 +7391,39 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7507,12 +7495,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7537,7 +7525,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7545,47 +7533,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7657,12 +7649,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7696,11 +7688,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7730,12 +7722,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7760,7 +7752,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7768,10 +7760,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7780,39 +7770,37 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7846,7 +7834,7 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7880,12 +7868,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7910,7 +7898,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7918,51 +7906,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7998,9 +7982,9 @@
       <c r="I100" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -8030,12 +8014,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8069,7 +8053,7 @@
         </is>
       </c>
       <c r="I101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -8103,12 +8087,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8133,7 +8117,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8141,8 +8125,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I102" s="2" t="n">
-        <v>3</v>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -8151,103 +8137,1917 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N118" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O118" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O119" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N120" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O120" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O121" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N122" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O122" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O123" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N124" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O124" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N125" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-043</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>Tombola</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N126" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O126" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>4078816754</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="n">
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L103" s="2" t="n">
+      <c r="L127" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M103" s="2" t="inlineStr">
+      <c r="M127" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N103" s="2" t="inlineStr">
+      <c r="N127" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O103" s="2" t="inlineStr">
+      <c r="O127" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O103"/>
+  <autoFilter ref="A1:O127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
+++ b/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,11 +33,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00008000"/>
+      <color rgb="00D93025"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00D93025"/>
+      <color rgb="00008000"/>
     </font>
   </fonts>
   <fills count="3">
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -597,47 +597,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -709,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -739,7 +743,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -747,8 +751,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n">
-        <v>1</v>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -757,37 +763,39 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -889,7 +897,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -897,47 +905,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1039,7 +1051,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1047,8 +1059,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n">
-        <v>1</v>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1057,37 +1071,39 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1189,7 +1205,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1197,8 +1213,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1207,37 +1225,39 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1339,55 +1359,59 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1489,7 +1513,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1497,47 +1521,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n">
-        <v>2</v>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>1</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1609,12 +1637,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1639,7 +1667,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1647,47 +1675,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1791,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1798,11 +1830,11 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1832,12 +1864,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1909,12 +1941,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1948,11 +1980,11 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1982,12 +2014,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,12 +2091,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2092,17 +2124,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2132,12 +2164,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2209,12 +2241,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2239,33 +2271,33 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 24,00</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -2282,12 +2314,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,12 +2391,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2389,7 +2421,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2398,24 +2430,24 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2432,12 +2464,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2509,12 +2541,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2550,9 +2582,9 @@
       <c r="I28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2582,12 +2614,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2659,12 +2691,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2698,11 +2730,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2732,12 +2764,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2809,12 +2841,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2852,7 +2884,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2882,12 +2914,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2959,12 +2991,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2998,11 +3030,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3032,12 +3064,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3062,7 +3094,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3070,8 +3102,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n">
-        <v>0</v>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
@@ -3080,37 +3114,39 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3146,9 +3182,9 @@
       <c r="I36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3178,12 +3214,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3208,7 +3244,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3216,8 +3252,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n">
-        <v>0</v>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3226,37 +3264,39 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3290,11 +3330,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3324,12 +3364,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3401,12 +3441,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3440,11 +3480,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3474,12 +3514,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3551,12 +3591,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3590,11 +3630,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3624,12 +3664,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3701,12 +3741,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3734,17 +3774,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3774,12 +3814,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3851,12 +3891,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3881,7 +3921,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3890,24 +3930,24 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L46" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -3924,12 +3964,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4001,12 +4041,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4040,11 +4080,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▲ 200,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4074,12 +4114,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4104,7 +4144,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4112,8 +4152,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n">
-        <v>0</v>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4122,37 +4164,39 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4186,7 +4230,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
@@ -4220,12 +4264,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4250,7 +4294,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -4258,8 +4302,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n">
-        <v>0</v>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
@@ -4268,37 +4314,39 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4323,7 +4371,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
@@ -4331,10 +4379,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4343,39 +4389,37 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4447,12 +4491,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4480,17 +4524,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4520,12 +4564,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4597,12 +4641,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4627,7 +4671,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4636,24 +4680,24 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4670,12 +4714,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4747,12 +4791,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4788,9 +4832,9 @@
       <c r="I58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4820,12 +4864,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4897,12 +4941,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4927,7 +4971,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4935,51 +4979,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5051,12 +5091,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5081,7 +5121,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5089,51 +5129,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I62" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5158,7 +5194,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5166,8 +5202,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n">
-        <v>0</v>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
@@ -5176,37 +5214,39 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5231,59 +5271,55 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5308,7 +5344,7 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -5316,47 +5352,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5381,7 +5421,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,00</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -5389,51 +5429,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I66" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>12,5%</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5458,7 +5494,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -5466,8 +5502,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n">
-        <v>1</v>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
@@ -5476,37 +5514,39 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5531,7 +5571,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5539,51 +5579,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I68" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5655,12 +5691,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5685,7 +5721,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5693,51 +5729,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I70" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5809,12 +5841,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5839,7 +5871,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5847,51 +5879,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I72" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5963,12 +5991,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -5993,7 +6021,7 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -6001,51 +6029,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I74" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6117,12 +6141,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6147,7 +6171,7 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
@@ -6155,51 +6179,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6224,7 +6244,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6232,10 +6252,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6244,39 +6262,37 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6301,7 +6317,7 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -6309,51 +6325,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I78" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6378,7 +6390,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6386,10 +6398,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6398,39 +6408,37 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6455,7 +6463,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6463,51 +6471,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6579,12 +6583,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6618,11 +6622,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6652,12 +6656,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6729,12 +6733,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6768,11 +6772,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6802,12 +6806,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6879,12 +6883,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6909,59 +6913,55 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -7071,51 +7071,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I88" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7187,12 +7183,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7217,7 +7213,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7225,51 +7221,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I90" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7294,7 +7286,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7302,10 +7294,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I91" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7314,39 +7304,37 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7371,7 +7359,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7379,10 +7367,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I92" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7391,39 +7377,37 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7448,7 +7432,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7456,10 +7440,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7468,39 +7450,37 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7572,12 +7552,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7649,12 +7629,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7722,12 +7702,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7752,7 +7732,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7760,8 +7740,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7770,37 +7752,39 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7836,9 +7820,9 @@
       <c r="I98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7868,12 +7852,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7898,7 +7882,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7906,47 +7890,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7980,7 +7968,7 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -8014,12 +8002,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8044,7 +8032,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -8052,8 +8040,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I101" s="2" t="n">
-        <v>1</v>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
@@ -8062,37 +8052,39 @@
       </c>
       <c r="K101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8164,12 +8156,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8241,12 +8233,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8318,12 +8310,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8348,7 +8340,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8356,10 +8348,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I105" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -8368,39 +8358,37 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8472,12 +8460,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8502,7 +8490,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8510,51 +8498,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8626,12 +8610,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8656,7 +8640,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8664,10 +8648,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I109" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
@@ -8676,39 +8658,37 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8780,12 +8760,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8857,12 +8837,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8887,7 +8867,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8895,8 +8875,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I112" s="2" t="n">
-        <v>0</v>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
@@ -8905,37 +8887,39 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9007,12 +8991,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9037,7 +9021,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -9045,47 +9029,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I114" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9157,12 +9145,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9187,7 +9175,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -9195,8 +9183,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I116" s="2" t="n">
-        <v>1</v>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
@@ -9205,37 +9195,39 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N116" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9307,12 +9299,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9337,7 +9329,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -9345,47 +9337,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I118" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L118" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N118" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9457,12 +9453,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9487,7 +9483,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -9495,47 +9491,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I120" s="2" t="n">
-        <v>1</v>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L120" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N120" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -9645,8 +9645,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I122" s="2" t="n">
-        <v>1</v>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
@@ -9655,37 +9657,39 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L122" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N122" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9757,12 +9761,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9798,9 +9802,9 @@
       <c r="I124" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -9830,12 +9834,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9860,7 +9864,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -9868,8 +9872,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I125" s="2" t="n">
-        <v>0</v>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
@@ -9878,37 +9884,39 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N125" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9942,7 +9950,7 @@
         </is>
       </c>
       <c r="I126" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -9976,78 +9984,3252 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-043</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
-        <is>
-          <t>Tombola</t>
-        </is>
-      </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>4078816754</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G127" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="n">
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J127" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L127" s="2" t="n">
+      <c r="L169" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M127" s="2" t="inlineStr">
+      <c r="M169" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N127" s="2" t="inlineStr">
+      <c r="N169" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O127" s="2" t="inlineStr">
+      <c r="O169" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O127"/>
+  <autoFilter ref="A1:O169"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
+++ b/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
@@ -661,7 +661,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1739,7 +1739,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -5489,7 +5489,7 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
@@ -6239,7 +6239,7 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
@@ -8181,7 +8181,7 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
@@ -8635,7 +8635,7 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
@@ -8939,7 +8939,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr">
@@ -10009,7 +10009,7 @@
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
@@ -11525,7 +11525,7 @@
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
@@ -11833,7 +11833,7 @@
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr">
@@ -11987,7 +11987,7 @@
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
@@ -12137,7 +12137,7 @@
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
@@ -12287,7 +12287,7 @@
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr">
@@ -12737,7 +12737,7 @@
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr">
@@ -12887,7 +12887,7 @@
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr">
@@ -13037,7 +13037,7 @@
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr">
@@ -13183,7 +13183,7 @@
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 24,90</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">

--- a/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
+++ b/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1637,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,14 +1791,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1829,8 +1829,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1839,37 +1841,39 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1941,12 +1945,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2014,12 +2018,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2091,12 +2095,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2132,9 +2136,9 @@
       <c r="I22" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -2164,12 +2168,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2241,14 +2245,14 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2274,17 +2278,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2314,12 +2318,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2391,14 +2395,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2421,33 +2425,33 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L26" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -2464,12 +2468,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2541,14 +2545,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2571,7 +2575,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2582,22 +2586,22 @@
       <c r="I28" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2614,12 +2618,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2691,14 +2695,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2730,11 +2734,11 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -2764,12 +2768,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2841,12 +2845,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2884,7 +2888,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2914,12 +2918,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2991,14 +2995,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3030,11 +3034,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3064,12 +3068,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3141,14 +3145,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3180,11 +3184,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3214,12 +3218,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3291,14 +3295,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3330,11 +3334,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3364,12 +3368,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3441,12 +3445,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3482,9 +3486,9 @@
       <c r="I40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3514,12 +3518,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3591,14 +3595,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3630,11 +3634,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3664,12 +3668,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3741,14 +3745,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3780,11 +3784,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3814,12 +3818,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3891,14 +3895,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3930,11 +3934,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3964,12 +3968,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4041,14 +4045,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4080,11 +4084,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4114,12 +4118,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4191,14 +4195,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4230,11 +4234,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4264,12 +4268,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4341,14 +4345,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4380,7 +4384,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
@@ -4414,12 +4418,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4491,14 +4495,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4524,17 +4528,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4564,12 +4568,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4641,14 +4645,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4671,33 +4675,33 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L56" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -4714,12 +4718,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4791,14 +4795,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4821,7 +4825,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4832,22 +4836,22 @@
       <c r="I58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4864,12 +4868,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4941,14 +4945,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4980,11 +4984,11 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -5014,12 +5018,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5091,14 +5095,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5130,11 +5134,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5164,12 +5168,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5241,14 +5245,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5274,17 +5278,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I64" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5314,12 +5318,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5391,14 +5395,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5421,33 +5425,33 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>R$ 24,00</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -5464,12 +5468,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5541,14 +5545,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5571,7 +5575,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 24,00</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -5582,22 +5586,22 @@
       <c r="I68" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5614,12 +5618,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5691,14 +5695,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5730,11 +5734,11 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -5764,12 +5768,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5841,12 +5845,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5882,9 +5886,9 @@
       <c r="I72" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5914,12 +5918,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5991,14 +5995,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6030,11 +6034,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6064,12 +6068,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6141,12 +6145,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6182,9 +6186,9 @@
       <c r="I76" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J76" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6214,14 +6218,14 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6244,7 +6248,7 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
@@ -6252,8 +6256,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n">
-        <v>0</v>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
@@ -6262,39 +6268,41 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6326,11 +6334,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6360,12 +6368,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6433,14 +6441,14 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6472,11 +6480,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6506,14 +6514,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6536,7 +6544,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6544,10 +6552,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6556,41 +6562,39 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6622,11 +6626,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6656,12 +6660,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6733,14 +6737,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6772,11 +6776,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6806,12 +6810,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6883,14 +6887,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6916,17 +6920,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6956,12 +6960,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7033,14 +7037,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7063,33 +7067,33 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L88" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr">
@@ -7106,12 +7110,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7183,14 +7187,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7213,7 +7217,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -7222,24 +7226,24 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7256,14 +7260,14 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7286,7 +7290,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7294,8 +7298,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n">
-        <v>0</v>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7304,39 +7310,41 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7368,11 +7376,11 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7402,12 +7410,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7475,14 +7483,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7505,7 +7513,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7513,10 +7521,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I94" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
@@ -7525,41 +7531,39 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7582,7 +7586,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7590,10 +7594,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7602,41 +7604,39 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7667,8 +7667,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="n">
-        <v>0</v>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7677,37 +7679,39 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7779,12 +7783,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7820,9 +7824,9 @@
       <c r="I98" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7852,12 +7856,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7929,14 +7933,14 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7968,11 +7972,11 @@
         </is>
       </c>
       <c r="I100" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -8002,12 +8006,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8079,14 +8083,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -8109,7 +8113,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8117,10 +8121,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I102" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
@@ -8129,39 +8131,37 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8233,12 +8233,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8310,14 +8310,14 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -8340,7 +8340,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8348,8 +8348,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I105" s="2" t="n">
-        <v>0</v>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -8358,37 +8360,39 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8460,12 +8464,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8501,9 +8505,9 @@
       <c r="I107" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -8533,12 +8537,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8610,14 +8614,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -8649,11 +8653,11 @@
         </is>
       </c>
       <c r="I109" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8683,12 +8687,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8760,14 +8764,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -8790,7 +8794,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8798,10 +8802,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I111" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8810,39 +8812,37 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9068,12 +9068,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9145,12 +9145,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9376,12 +9376,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9453,12 +9453,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9530,12 +9530,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9761,14 +9761,14 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H124" s="2" t="inlineStr">
@@ -9799,8 +9799,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I124" s="2" t="n">
-        <v>0</v>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
@@ -9809,37 +9811,39 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L124" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N124" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9911,12 +9915,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9984,12 +9988,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10061,14 +10065,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -10091,7 +10095,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -10099,10 +10103,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I128" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
@@ -10111,39 +10113,37 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L128" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10215,12 +10215,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10292,12 +10292,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10446,12 +10446,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10754,12 +10754,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10831,14 +10831,14 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -10861,7 +10861,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -10869,8 +10869,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I138" s="2" t="n">
-        <v>0</v>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -10879,39 +10881,41 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -10934,7 +10938,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -10942,8 +10946,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I139" s="2" t="n">
-        <v>0</v>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
@@ -10952,37 +10958,39 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L139" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N139" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11050,12 +11058,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11091,9 +11099,9 @@
       <c r="I141" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -11123,12 +11131,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11196,14 +11204,14 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -11235,11 +11243,11 @@
         </is>
       </c>
       <c r="I143" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J143" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11269,14 +11277,14 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -11299,7 +11307,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -11307,10 +11315,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I144" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -11319,41 +11325,39 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L144" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -11376,7 +11380,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -11384,10 +11388,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I145" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
@@ -11396,39 +11398,37 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11577,12 +11577,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11654,12 +11654,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11731,12 +11731,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11808,12 +11808,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11885,12 +11885,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11962,12 +11962,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12039,14 +12039,14 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -12077,8 +12077,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I154" s="2" t="n">
-        <v>0</v>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
@@ -12087,37 +12089,39 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L154" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12189,12 +12193,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12230,9 +12234,9 @@
       <c r="I156" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -12262,12 +12266,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12339,14 +12343,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -12378,11 +12382,11 @@
         </is>
       </c>
       <c r="I158" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J158" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12412,12 +12416,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12489,14 +12493,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -12528,11 +12532,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12562,12 +12566,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12639,14 +12643,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -12678,11 +12682,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12712,12 +12716,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12789,12 +12793,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12832,7 +12836,7 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12862,12 +12866,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12939,14 +12943,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -12978,11 +12982,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -13012,14 +13016,14 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -13042,7 +13046,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -13050,8 +13054,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I167" s="2" t="n">
-        <v>0</v>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
@@ -13060,39 +13066,41 @@
       </c>
       <c r="K167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L167" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M167" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N167" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -13124,11 +13132,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J168" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -13158,12 +13166,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13228,8 +13236,154 @@
         </is>
       </c>
     </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
+++ b/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1637,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1945,14 +1945,14 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1983,8 +1983,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
@@ -1993,37 +1995,39 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2095,12 +2099,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2168,12 +2172,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2245,12 +2249,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2286,9 +2290,9 @@
       <c r="I24" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2318,12 +2322,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2395,14 +2399,14 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2428,17 +2432,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2468,12 +2472,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2545,14 +2549,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2575,33 +2579,33 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -2618,12 +2622,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2695,14 +2699,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2725,7 +2729,7 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2736,22 +2740,22 @@
       <c r="I30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J30" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2768,12 +2772,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2845,14 +2849,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2884,11 +2888,11 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -2918,12 +2922,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2995,12 +2999,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3038,7 +3042,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3068,12 +3072,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3145,14 +3149,14 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3184,11 +3188,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3218,12 +3222,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3295,14 +3299,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3334,11 +3338,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3368,12 +3372,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3445,14 +3449,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3484,11 +3488,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3518,12 +3522,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3595,12 +3599,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3636,9 +3640,9 @@
       <c r="I42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3668,12 +3672,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3745,14 +3749,14 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3784,11 +3788,11 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3818,12 +3822,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3895,14 +3899,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3934,11 +3938,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3968,12 +3972,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4045,14 +4049,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4084,11 +4088,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4118,12 +4122,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4195,14 +4199,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4234,11 +4238,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4268,12 +4272,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4345,14 +4349,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4384,11 +4388,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4418,12 +4422,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4495,14 +4499,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4534,7 +4538,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
@@ -4568,12 +4572,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4645,14 +4649,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4678,17 +4682,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4718,12 +4722,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4795,14 +4799,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4825,33 +4829,33 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -4868,12 +4872,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4945,14 +4949,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4975,7 +4979,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4986,22 +4990,22 @@
       <c r="I60" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -5018,12 +5022,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5095,14 +5099,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5134,11 +5138,11 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -5168,12 +5172,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5245,14 +5249,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5284,11 +5288,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5318,12 +5322,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5395,14 +5399,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5428,17 +5432,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5468,12 +5472,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5545,14 +5549,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5575,33 +5579,33 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>R$ 24,00</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L68" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -5618,12 +5622,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5695,14 +5699,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5725,7 +5729,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 24,00</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5736,22 +5740,22 @@
       <c r="I70" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5768,12 +5772,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5845,14 +5849,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5884,11 +5888,11 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -5918,12 +5922,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5995,12 +5999,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6036,9 +6040,9 @@
       <c r="I74" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6068,12 +6072,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6145,14 +6149,14 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6184,11 +6188,11 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6218,12 +6222,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6295,12 +6299,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6336,9 +6340,9 @@
       <c r="I78" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6368,14 +6372,14 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6398,7 +6402,7 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -6406,8 +6410,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n">
-        <v>0</v>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
@@ -6416,39 +6422,41 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6480,11 +6488,11 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6514,12 +6522,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6587,14 +6595,14 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6626,11 +6634,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6660,14 +6668,14 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6690,7 +6698,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6698,10 +6706,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6710,41 +6716,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6776,11 +6780,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6810,12 +6814,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6887,14 +6891,14 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6926,11 +6930,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J86" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J86" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6960,12 +6964,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7037,14 +7041,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7070,17 +7074,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7110,12 +7114,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7187,14 +7191,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7217,33 +7221,33 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -7260,12 +7264,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7337,14 +7341,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7367,7 +7371,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -7376,24 +7380,24 @@
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7410,14 +7414,14 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7440,7 +7444,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7448,8 +7452,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n">
-        <v>0</v>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7458,39 +7464,41 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7522,11 +7530,11 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7556,12 +7564,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7629,14 +7637,14 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7659,7 +7667,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -7667,10 +7675,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I96" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
@@ -7679,41 +7685,39 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7736,7 +7740,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7744,10 +7748,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7756,41 +7758,39 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7813,7 +7813,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7821,8 +7821,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I98" s="2" t="n">
-        <v>0</v>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7831,37 +7833,39 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7933,12 +7937,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7974,9 +7978,9 @@
       <c r="I100" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -8006,12 +8010,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8083,14 +8087,14 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -8122,11 +8126,11 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8156,12 +8160,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8233,14 +8237,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -8263,7 +8267,7 @@
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -8271,10 +8275,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I104" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -8283,39 +8285,37 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8387,12 +8387,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8464,14 +8464,14 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8502,8 +8502,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I107" s="2" t="n">
-        <v>0</v>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -8512,37 +8514,39 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8614,12 +8618,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8655,9 +8659,9 @@
       <c r="I109" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -8687,12 +8691,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8764,14 +8768,14 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -8803,11 +8807,11 @@
         </is>
       </c>
       <c r="I111" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J111" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8837,12 +8841,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8914,14 +8918,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -8944,7 +8948,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -8952,10 +8956,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I113" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
@@ -8964,39 +8966,37 @@
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9068,12 +9068,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9145,12 +9145,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9376,12 +9376,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9453,12 +9453,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9530,12 +9530,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9761,12 +9761,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9838,12 +9838,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9915,14 +9915,14 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -9953,8 +9953,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I126" s="2" t="n">
-        <v>0</v>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
@@ -9963,37 +9965,39 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L126" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N126" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10065,12 +10069,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10138,12 +10142,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10215,14 +10219,14 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -10245,7 +10249,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -10253,10 +10257,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -10265,39 +10267,37 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L130" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10446,12 +10446,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10754,12 +10754,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10985,14 +10985,14 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -11015,7 +11015,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -11023,8 +11023,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I140" s="2" t="n">
-        <v>0</v>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -11033,39 +11035,41 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L140" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -11088,7 +11092,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">
@@ -11096,8 +11100,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I141" s="2" t="n">
-        <v>0</v>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
@@ -11106,37 +11112,39 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L141" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N141" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11204,12 +11212,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11245,9 +11253,9 @@
       <c r="I143" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -11277,12 +11285,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11350,14 +11358,14 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -11389,11 +11397,11 @@
         </is>
       </c>
       <c r="I145" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J145" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11423,14 +11431,14 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -11453,7 +11461,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -11461,10 +11469,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I146" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
@@ -11473,41 +11479,39 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L146" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -11530,7 +11534,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -11538,10 +11542,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I147" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
@@ -11550,39 +11552,37 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11654,12 +11654,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11731,12 +11731,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11808,12 +11808,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11885,12 +11885,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11962,12 +11962,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12039,12 +12039,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12116,12 +12116,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12193,14 +12193,14 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -12223,7 +12223,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -12231,8 +12231,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I156" s="2" t="n">
-        <v>0</v>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
@@ -12241,37 +12243,39 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L156" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12343,12 +12347,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12384,9 +12388,9 @@
       <c r="I158" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -12416,12 +12420,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12493,14 +12497,14 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -12532,11 +12536,11 @@
         </is>
       </c>
       <c r="I160" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J160" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12566,12 +12570,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12643,14 +12647,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -12682,11 +12686,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12716,12 +12720,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12793,14 +12797,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -12832,11 +12836,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J164" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12866,12 +12870,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12943,12 +12947,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12986,7 +12990,7 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -13016,12 +13020,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13093,14 +13097,14 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -13132,11 +13136,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -13166,14 +13170,14 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -13196,7 +13200,7 @@
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H169" s="2" t="inlineStr">
@@ -13204,8 +13208,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I169" s="2" t="n">
-        <v>0</v>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
@@ -13214,39 +13220,41 @@
       </c>
       <c r="K169" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M169" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N169" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -13278,11 +13286,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -13312,12 +13320,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13382,8 +13390,154 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
+++ b/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -944,12 +944,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1175,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1329,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1637,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,12 +1791,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2099,14 +2099,14 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
-        </is>
-      </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2137,8 +2137,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
@@ -2147,37 +2149,39 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2249,12 +2253,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2322,12 +2326,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2399,12 +2403,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2440,9 +2444,9 @@
       <c r="I26" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -2472,12 +2476,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2549,14 +2553,14 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
-        </is>
-      </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2582,17 +2586,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -2622,12 +2626,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2699,14 +2703,14 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
-        </is>
-      </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2729,33 +2733,33 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -2772,12 +2776,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2849,14 +2853,14 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
-        </is>
-      </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -2879,7 +2883,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2890,22 +2894,22 @@
       <c r="I32" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2922,12 +2926,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2999,14 +3003,14 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
-        </is>
-      </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3038,11 +3042,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3072,12 +3076,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3149,12 +3153,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3192,7 +3196,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3222,12 +3226,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3299,14 +3303,14 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
-        </is>
-      </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3338,11 +3342,11 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3372,12 +3376,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3449,14 +3453,14 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
-        </is>
-      </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3488,11 +3492,11 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -3522,12 +3526,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3599,14 +3603,14 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
-        </is>
-      </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3638,11 +3642,11 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -3672,12 +3676,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3749,12 +3753,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3790,9 +3794,9 @@
       <c r="I44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -3822,12 +3826,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3899,14 +3903,14 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
-        </is>
-      </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -3938,11 +3942,11 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3972,12 +3976,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4049,14 +4053,14 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
-        </is>
-      </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4088,11 +4092,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4122,12 +4126,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4199,14 +4203,14 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
-        </is>
-      </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4238,11 +4242,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4272,12 +4276,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4349,14 +4353,14 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
-        </is>
-      </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4388,11 +4392,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4422,12 +4426,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4499,14 +4503,14 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
-        </is>
-      </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4538,11 +4542,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4572,12 +4576,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4649,14 +4653,14 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
-        </is>
-      </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4688,7 +4692,7 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
@@ -4722,12 +4726,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4799,14 +4803,14 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
-        </is>
-      </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4832,17 +4836,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I58" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4872,12 +4876,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4949,14 +4953,14 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
-        </is>
-      </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -4979,33 +4983,33 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L60" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -5022,12 +5026,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5099,14 +5103,14 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
-        </is>
-      </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5129,7 +5133,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5140,22 +5144,22 @@
       <c r="I62" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5172,12 +5176,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5249,14 +5253,14 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
-        </is>
-      </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5288,11 +5292,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5322,12 +5326,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5399,14 +5403,14 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
-        </is>
-      </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5438,11 +5442,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>1</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5472,12 +5476,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5549,14 +5553,14 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
-        </is>
-      </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5582,17 +5586,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5622,12 +5626,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5699,14 +5703,14 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
-        </is>
-      </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5729,33 +5733,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 24,00</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5772,12 +5776,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5849,14 +5853,14 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
-        </is>
-      </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -5879,7 +5883,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 24,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5890,22 +5894,22 @@
       <c r="I72" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5922,12 +5926,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -5999,14 +6003,14 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
-        </is>
-      </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6038,11 +6042,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>8</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6072,12 +6076,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6149,12 +6153,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6190,9 +6194,9 @@
       <c r="I76" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -6222,12 +6226,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6299,14 +6303,14 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
-        </is>
-      </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6338,11 +6342,11 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6372,12 +6376,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6449,12 +6453,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6490,9 +6494,9 @@
       <c r="I80" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -6522,14 +6526,14 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
-        </is>
-      </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6552,7 +6556,7 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -6560,8 +6564,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n">
-        <v>0</v>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
@@ -6570,39 +6576,41 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6634,11 +6642,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6668,12 +6676,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6741,14 +6749,14 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6780,11 +6788,11 @@
         </is>
       </c>
       <c r="I84" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6814,14 +6822,14 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
-        </is>
-      </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6844,7 +6852,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6852,10 +6860,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6864,41 +6870,39 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
-        </is>
-      </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -6930,11 +6934,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>▼ 16,7%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6964,12 +6968,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7041,14 +7045,14 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
-        </is>
-      </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7080,11 +7084,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7114,12 +7118,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7191,14 +7195,14 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
-        </is>
-      </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7224,17 +7228,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H90" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>6</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7264,12 +7268,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7341,14 +7345,14 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
-        </is>
-      </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7371,33 +7375,33 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H92" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L92" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -7414,12 +7418,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7491,14 +7495,14 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7521,7 +7525,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7530,24 +7534,24 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7564,14 +7568,14 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
-        </is>
-      </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7594,7 +7598,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -7602,8 +7606,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n">
-        <v>0</v>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
@@ -7612,39 +7618,41 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
-        </is>
-      </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7676,11 +7684,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7710,12 +7718,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7783,14 +7791,14 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7813,7 +7821,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -7821,10 +7829,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I98" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
@@ -7833,41 +7839,39 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
-        </is>
-      </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7890,7 +7894,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7898,10 +7902,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7910,41 +7912,39 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
-        </is>
-      </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -7975,8 +7975,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I100" s="2" t="n">
-        <v>0</v>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
@@ -7985,37 +7987,39 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8087,12 +8091,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8128,9 +8132,9 @@
       <c r="I102" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -8160,12 +8164,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8237,14 +8241,14 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
-        </is>
-      </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -8276,11 +8280,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8310,12 +8314,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8387,14 +8391,14 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
-        </is>
-      </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -8417,7 +8421,7 @@
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
@@ -8425,10 +8429,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I106" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -8437,39 +8439,37 @@
       </c>
       <c r="K106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L106" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8618,14 +8618,14 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
-        </is>
-      </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -8648,7 +8648,7 @@
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
@@ -8656,8 +8656,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I109" s="2" t="n">
-        <v>0</v>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
@@ -8666,37 +8668,39 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L109" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N109" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8768,12 +8772,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8809,9 +8813,9 @@
       <c r="I111" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -8841,12 +8845,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8918,14 +8922,14 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
-        </is>
-      </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -8957,11 +8961,11 @@
         </is>
       </c>
       <c r="I113" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -8991,12 +8995,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9068,14 +9072,14 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
-        </is>
-      </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -9098,7 +9102,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -9106,10 +9110,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I115" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -9118,39 +9120,37 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9376,12 +9376,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9453,12 +9453,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9530,12 +9530,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9607,12 +9607,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9761,12 +9761,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9838,12 +9838,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9915,12 +9915,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10069,14 +10069,14 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
-        </is>
-      </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -10099,7 +10099,7 @@
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr">
@@ -10107,8 +10107,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I128" s="2" t="n">
-        <v>0</v>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
@@ -10117,37 +10119,39 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L128" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N128" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10219,12 +10223,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10292,12 +10296,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10369,14 +10373,14 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
-        </is>
-      </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -10399,7 +10403,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10407,10 +10411,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I132" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -10419,39 +10421,37 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10754,12 +10754,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11062,12 +11062,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11139,14 +11139,14 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -11177,8 +11177,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I142" s="2" t="n">
-        <v>0</v>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
@@ -11187,39 +11189,41 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L142" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N142" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
-        </is>
-      </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -11242,7 +11246,7 @@
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -11250,8 +11254,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I143" s="2" t="n">
-        <v>0</v>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
@@ -11260,37 +11266,39 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L143" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N143" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11358,12 +11366,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11399,9 +11407,9 @@
       <c r="I145" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -11431,12 +11439,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11504,14 +11512,14 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
-        </is>
-      </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -11543,11 +11551,11 @@
         </is>
       </c>
       <c r="I147" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J147" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -11577,14 +11585,14 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -11607,7 +11615,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -11615,10 +11623,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I148" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -11627,41 +11633,39 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L148" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
-        </is>
-      </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -11684,7 +11688,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11692,10 +11696,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I149" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -11704,39 +11706,37 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11808,12 +11808,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11885,12 +11885,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11962,12 +11962,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12039,12 +12039,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12116,12 +12116,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12270,12 +12270,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12347,14 +12347,14 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -12377,7 +12377,7 @@
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr">
@@ -12385,8 +12385,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I158" s="2" t="n">
-        <v>0</v>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
@@ -12395,37 +12397,39 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L158" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N158" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12497,12 +12501,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12538,9 +12542,9 @@
       <c r="I160" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -12570,12 +12574,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12647,14 +12651,14 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
-        </is>
-      </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -12686,11 +12690,11 @@
         </is>
       </c>
       <c r="I162" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J162" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -12720,12 +12724,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12797,14 +12801,14 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
-        </is>
-      </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -12836,11 +12840,11 @@
         </is>
       </c>
       <c r="I164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -12870,12 +12874,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12947,14 +12951,14 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
-        </is>
-      </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -12986,11 +12990,11 @@
         </is>
       </c>
       <c r="I166" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J166" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -13020,12 +13024,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13097,12 +13101,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13140,7 +13144,7 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -13170,12 +13174,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13247,14 +13251,14 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -13286,11 +13290,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -13320,14 +13324,14 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
-        </is>
-      </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -13350,7 +13354,7 @@
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H171" s="2" t="inlineStr">
@@ -13358,8 +13362,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I171" s="2" t="n">
-        <v>0</v>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
@@ -13368,39 +13374,41 @@
       </c>
       <c r="K171" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M171" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N171" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
           <t>BRINQ-043</t>
@@ -13432,11 +13440,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J172" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13466,12 +13474,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13536,8 +13544,154 @@
         </is>
       </c>
     </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
+++ b/saida_skus/SKU_BRINQ-043-TOMBOLA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -636,12 +636,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -751,10 +751,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
@@ -763,39 +761,37 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -867,12 +863,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -897,7 +893,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -905,51 +901,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1021,12 +1013,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1051,7 +1043,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1059,10 +1051,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
@@ -1071,39 +1061,37 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1175,12 +1163,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1252,12 +1240,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1329,12 +1317,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1406,12 +1394,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1483,12 +1471,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1560,12 +1548,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1637,12 +1625,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1714,12 +1702,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1791,12 +1779,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1868,12 +1856,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1945,12 +1933,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2022,12 +2010,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2099,12 +2087,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2176,12 +2164,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2253,12 +2241,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2283,7 +2271,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2291,8 +2279,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
@@ -2301,37 +2291,39 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2403,12 +2395,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2433,7 +2425,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2441,8 +2433,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>0</v>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2451,37 +2445,39 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2553,12 +2549,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2583,7 +2579,7 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -2591,47 +2587,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2703,12 +2703,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2733,55 +2733,59 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2853,12 +2857,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2883,7 +2887,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2892,24 +2896,24 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>33,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L32" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -2926,12 +2930,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3003,12 +3007,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3042,11 +3046,11 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -3076,12 +3080,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3153,12 +3157,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3192,11 +3196,11 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -3226,12 +3230,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3303,12 +3307,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3336,17 +3340,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -3376,12 +3380,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3453,12 +3457,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3483,7 +3487,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 25,00</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3492,24 +3496,24 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>33,3%</t>
         </is>
       </c>
       <c r="L40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -3526,12 +3530,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3603,12 +3607,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3676,12 +3680,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3753,12 +3757,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3826,12 +3830,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3903,12 +3907,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3944,9 +3948,9 @@
       <c r="I46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -3976,12 +3980,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4053,12 +4057,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4092,11 +4096,11 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>▼ 50,0%</t>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -4126,12 +4130,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4203,12 +4207,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4242,11 +4246,11 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>▲ 100,0%</t>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -4276,12 +4280,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4353,12 +4357,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4392,11 +4396,11 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -4426,12 +4430,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4503,12 +4507,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4542,11 +4546,11 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -4576,12 +4580,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4653,12 +4657,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4694,9 +4698,9 @@
       <c r="I56" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -4726,12 +4730,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4803,12 +4807,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4842,11 +4846,11 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -4876,12 +4880,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4953,12 +4957,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4986,17 +4990,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -5026,12 +5030,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5103,12 +5107,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5133,7 +5137,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>R$ 25,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -5142,24 +5146,24 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L62" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -5176,12 +5180,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5253,12 +5257,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5292,11 +5296,11 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t>▲ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -5326,12 +5330,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5403,12 +5407,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5442,11 +5446,11 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>0</v>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -5476,12 +5480,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5553,12 +5557,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5586,17 +5590,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -5626,12 +5630,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5703,12 +5707,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5733,33 +5737,33 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+          <t>R$ 25,00</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J70" s="3" t="inlineStr">
-        <is>
-          <t>▼ 75,0%</t>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
@@ -5776,12 +5780,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5853,12 +5857,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5883,7 +5887,7 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>R$ 24,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5892,24 +5896,24 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>2</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>▲ 100,0%</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L72" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -5926,12 +5930,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6003,12 +6007,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6042,11 +6046,11 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>▲ 166,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -6076,12 +6080,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6153,12 +6157,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6192,7 +6196,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
@@ -6226,12 +6230,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6303,12 +6307,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6336,17 +6340,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J78" s="4" t="inlineStr">
-        <is>
-          <t>▲ 50,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J78" s="3" t="inlineStr">
+        <is>
+          <t>▼ 75,0%</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -6376,12 +6380,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6453,12 +6457,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6483,7 +6487,7 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 24,00</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
@@ -6492,7 +6496,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
@@ -6501,15 +6505,15 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="L80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -6526,12 +6530,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6603,12 +6607,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6642,11 +6646,11 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J82" s="3" t="inlineStr">
-        <is>
-          <t>▼ 33,3%</t>
+        <v>8</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>▲ 166,7%</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -6676,12 +6680,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6706,7 +6710,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -6714,8 +6718,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n">
-        <v>0</v>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
@@ -6724,37 +6730,39 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6790,9 +6798,9 @@
       <c r="I84" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -6822,12 +6830,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6852,7 +6860,7 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -6860,8 +6868,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n">
-        <v>0</v>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
@@ -6870,37 +6880,39 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -6934,11 +6946,11 @@
         </is>
       </c>
       <c r="I86" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>▼ 80,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>▲ 50,0%</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6968,12 +6980,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7045,12 +7057,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7084,11 +7096,11 @@
         </is>
       </c>
       <c r="I88" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>▼ 16,7%</t>
+        <v>2</v>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -7118,12 +7130,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7195,12 +7207,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7234,11 +7246,11 @@
         </is>
       </c>
       <c r="I90" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
+        <is>
+          <t>▼ 33,3%</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -7268,12 +7280,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7298,7 +7310,7 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
@@ -7306,10 +7318,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I91" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
@@ -7318,39 +7328,37 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7378,17 +7386,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H92" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I92" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>3</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -7418,12 +7426,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7448,7 +7456,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -7456,10 +7464,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7468,39 +7474,37 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7525,7 +7529,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>R$ 50,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -7534,24 +7538,24 @@
         </is>
       </c>
       <c r="I94" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>▼ 66,7%</t>
+          <t>▼ 80,0%</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L94" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr">
@@ -7568,12 +7572,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7645,12 +7649,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7684,11 +7688,11 @@
         </is>
       </c>
       <c r="I96" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
-        <is>
-          <t>▲ 200,0%</t>
+        <v>5</v>
+      </c>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>▼ 16,7%</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7718,12 +7722,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7748,7 +7752,7 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
@@ -7756,8 +7760,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n">
-        <v>0</v>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
@@ -7766,37 +7772,39 @@
       </c>
       <c r="K97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7830,11 +7838,11 @@
         </is>
       </c>
       <c r="I98" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>6</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7864,12 +7872,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7894,7 +7902,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -7902,8 +7910,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I99" s="2" t="n">
-        <v>0</v>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
@@ -7912,37 +7922,39 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -7967,59 +7979,55 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8091,12 +8099,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8121,7 +8129,7 @@
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 50,00</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
@@ -8130,24 +8138,24 @@
         </is>
       </c>
       <c r="I102" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
@@ -8164,12 +8172,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8241,12 +8249,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8280,11 +8288,11 @@
         </is>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>6</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>▲ 200,0%</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -8314,12 +8322,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8344,7 +8352,7 @@
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
@@ -8352,10 +8360,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I105" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -8364,39 +8370,37 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L105" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8464,12 +8468,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8494,7 +8498,7 @@
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
@@ -8502,10 +8506,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I107" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -8514,39 +8516,37 @@
       </c>
       <c r="K107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8695,12 +8695,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
@@ -8733,10 +8733,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I110" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
@@ -8745,39 +8743,37 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8802,7 +8798,7 @@
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
@@ -8810,8 +8806,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I111" s="2" t="n">
-        <v>0</v>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
@@ -8820,37 +8818,39 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L111" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -8883,51 +8883,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L112" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -8952,7 +8948,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -8960,47 +8956,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I113" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L113" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N113" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9025,7 +9025,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -9033,10 +9033,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I114" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
@@ -9045,39 +9043,37 @@
       </c>
       <c r="K114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9102,7 +9098,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -9110,8 +9106,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I115" s="2" t="n">
-        <v>1</v>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
@@ -9120,37 +9118,39 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N115" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9376,12 +9376,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -9414,10 +9414,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I119" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
@@ -9426,39 +9424,37 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L119" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9530,12 +9526,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9560,7 +9556,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -9568,51 +9564,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L121" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9684,12 +9676,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9714,7 +9706,7 @@
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H123" s="2" t="inlineStr">
@@ -9722,10 +9714,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I123" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
@@ -9734,39 +9724,37 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L123" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9838,12 +9826,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -9915,12 +9903,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -9992,12 +9980,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10069,12 +10057,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10146,12 +10134,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10223,12 +10211,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10253,7 +10241,7 @@
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H130" s="2" t="inlineStr">
@@ -10261,8 +10249,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I130" s="2" t="n">
-        <v>0</v>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
@@ -10271,37 +10261,39 @@
       </c>
       <c r="K130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L130" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N130" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10373,12 +10365,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10403,7 +10395,7 @@
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H132" s="2" t="inlineStr">
@@ -10411,8 +10403,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I132" s="2" t="n">
-        <v>0</v>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
@@ -10421,37 +10415,39 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L132" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N132" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10523,12 +10519,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10600,12 +10596,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10677,12 +10673,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10754,12 +10750,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10831,12 +10827,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -10861,7 +10857,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -10869,10 +10865,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I138" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
@@ -10881,39 +10875,37 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -10985,12 +10977,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11015,7 +11007,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -11023,10 +11015,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I140" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -11035,39 +11025,37 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L140" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11139,12 +11127,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11216,12 +11204,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11293,12 +11281,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11323,7 +11311,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -11331,8 +11319,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I144" s="2" t="n">
-        <v>0</v>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
@@ -11341,37 +11331,39 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L144" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N144" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11396,7 +11388,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -11404,8 +11396,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I145" s="2" t="n">
-        <v>0</v>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
@@ -11414,37 +11408,39 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L145" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N145" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11469,7 +11465,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -11477,8 +11473,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I146" s="2" t="n">
-        <v>0</v>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
@@ -11487,37 +11485,39 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L146" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N146" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -11550,47 +11550,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I147" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L147" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N147" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11615,7 +11619,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -11623,8 +11627,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I148" s="2" t="n">
-        <v>0</v>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
@@ -11633,37 +11639,39 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L148" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N148" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11688,7 +11696,7 @@
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H149" s="2" t="inlineStr">
@@ -11696,8 +11704,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I149" s="2" t="n">
-        <v>1</v>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
@@ -11706,37 +11716,39 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L149" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N149" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11808,12 +11820,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -11885,12 +11897,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -11915,7 +11927,7 @@
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H152" s="2" t="inlineStr">
@@ -11923,10 +11935,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I152" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
@@ -11935,39 +11945,37 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L152" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L152" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -11992,7 +12000,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -12000,10 +12008,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I153" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
@@ -12012,39 +12018,37 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L153" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12069,7 +12073,7 @@
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -12077,10 +12081,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I154" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
@@ -12089,39 +12091,37 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L154" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L154" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N154" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -12154,51 +12154,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L155" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L155" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12223,7 +12219,7 @@
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr">
@@ -12231,10 +12227,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I156" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
@@ -12243,39 +12237,37 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L156" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L156" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N156" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12300,7 +12292,7 @@
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H157" s="2" t="inlineStr">
@@ -12308,10 +12300,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I157" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
@@ -12320,39 +12310,37 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L157" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L157" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Boa</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12424,12 +12412,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12501,12 +12489,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12531,7 +12519,7 @@
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H160" s="2" t="inlineStr">
@@ -12539,8 +12527,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I160" s="2" t="n">
-        <v>0</v>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
@@ -12549,37 +12539,39 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L160" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N160" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12651,12 +12643,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12681,7 +12673,7 @@
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
@@ -12689,47 +12681,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I162" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L162" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N162" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12801,12 +12797,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -12831,7 +12827,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -12839,8 +12835,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I164" s="2" t="n">
-        <v>1</v>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
@@ -12849,37 +12847,39 @@
       </c>
       <c r="K164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L164" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M164" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N164" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H166" s="2" t="inlineStr">
@@ -12989,47 +12989,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I166" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J166" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L166" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M166" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N166" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13101,12 +13105,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13140,11 +13144,11 @@
         </is>
       </c>
       <c r="I168" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -13174,12 +13178,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13251,12 +13255,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13290,11 +13294,11 @@
         </is>
       </c>
       <c r="I170" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J170" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -13324,12 +13328,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13401,12 +13405,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13440,11 +13444,11 @@
         </is>
       </c>
       <c r="I172" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J172" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -13474,12 +13478,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13504,7 +13508,7 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
@@ -13512,8 +13516,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I173" s="2" t="n">
-        <v>0</v>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
@@ -13522,37 +13528,39 @@
       </c>
       <c r="K173" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="n">
-        <v>0</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N173" s="2" t="inlineStr">
         <is>
-          <t>Básica</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
-          <t>Boa</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13586,11 +13594,11 @@
         </is>
       </c>
       <c r="I174" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>0</v>
+      </c>
+      <c r="J174" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -13620,78 +13628,674 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>4078816754</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>Básica</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>BRINQ-043</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Tombola</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>4654751810</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>Sem calcular</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>Boa</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>BRINQ-043</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Tombola</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>4078816754</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 24,90</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 24,90</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
         <is>
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="n">
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L175" s="2" t="n">
+      <c r="L183" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="M175" s="2" t="inlineStr">
+      <c r="M183" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="N175" s="2" t="inlineStr">
+      <c r="N183" s="2" t="inlineStr">
         <is>
           <t>Básica</t>
         </is>
       </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>Boa</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>